--- a/MVP-1/SRS/FlatWire_OrderAllocationExamples.xlsx
+++ b/MVP-1/SRS/FlatWire_OrderAllocationExamples.xlsx
@@ -7145,7 +7145,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>R00002D</t>
+          <t>R00002AA</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -7180,7 +7180,7 @@
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t>One parent - this coil is entirely the incoming rod.</t>
+          <t>One rod, so one identity. The identity is built from the part of the rod this coil was cut from, R00002A, which is why it carries two letters where a spool part carries one.</t>
         </is>
       </c>
     </row>
@@ -7192,7 +7192,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>R00002E</t>
+          <t>R00002AB</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -7227,13 +7227,17 @@
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>The weld falls inside this coil, so it has two parents and its certificate names both.</t>
+          <t>The weld falls inside this coil, so it comes from two rods and carries an identity for each. This one covers the 500 lb from R00002 and is built from the same rod part as coil 1, R00002A, taking the next free letter.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr"/>
-      <c r="B14" s="4" t="inlineStr"/>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>R00001CA</t>
+        </is>
+      </c>
       <c r="C14" s="4" t="inlineStr"/>
       <c r="D14" s="4" t="inlineStr"/>
       <c r="E14" s="4" t="inlineStr">
@@ -7258,7 +7262,7 @@
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>The weld falls inside this coil, so it has two parents and its certificate names both.</t>
+          <t>And this one covers the 400 lb from R00001. It is built from that rod's part R00001C, and it is the first coil off that part, so it takes the first letter. This is the same pairing your own planning sheet writes as R00002AA - R00001CA. Both identities go into the coil records your other systems read, each carrying only its own weight, so the two add up to the coil's 900 lb and nothing is counted twice.</t>
         </is>
       </c>
     </row>
